--- a/VanEck/VanEck-KostenBepaling2020.xlsx
+++ b/VanEck/VanEck-KostenBepaling2020.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GoogleDrive\Financieel\Aandelen\KeuzeWelkIndexFonds\PerFonds\VanEck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF575736-953F-421F-9F3D-061A3DB8AA46}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C7825C-7BCF-4FD5-BFFB-5E0393C98FB3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,13 +156,13 @@
     <t>Houden dividend in cash totdat wordt uitgekeerd. Zorgt voor drag in opgaande markt</t>
   </si>
   <si>
-    <t>0,13% lijkt wat voor hiervoor, maar volgens VanEck is dit wel zo</t>
-  </si>
-  <si>
     <t>Ik dacht dat aan eventueel beetje lek lag, maar schijnt nihil te zijn volgens VanEck</t>
   </si>
   <si>
     <t>Komt door cash/tax drag, waarvan cash drag van ongeinvesteerd dividend grootste component is</t>
+  </si>
+  <si>
+    <t>0,13% lijkt wat veel voor hiervoor, maar volgens VanEck is dit wel zo</t>
   </si>
 </sst>
 </file>
@@ -255,7 +255,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -287,6 +287,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Procent" xfId="1" builtinId="5"/>
@@ -836,23 +837,23 @@
         <v>332017</v>
       </c>
       <c r="D13" s="19">
-        <f t="shared" ref="D13:H13" si="0">SUM(D10:D12)</f>
+        <f>SUM(D10:D12)</f>
         <v>613246</v>
       </c>
       <c r="E13" s="19">
-        <f t="shared" si="0"/>
+        <f>SUM(E10:E12)</f>
         <v>864920</v>
       </c>
       <c r="F13" s="19">
-        <f t="shared" si="0"/>
+        <f>SUM(F10:F12)</f>
         <v>1009909</v>
       </c>
       <c r="G13" s="19">
-        <f t="shared" si="0"/>
+        <f>SUM(G10:G12)</f>
         <v>1241913</v>
       </c>
       <c r="H13" s="19">
-        <f t="shared" si="0"/>
+        <f>SUM(H10:H12)</f>
         <v>1513230</v>
       </c>
       <c r="I13" s="18"/>
@@ -870,68 +871,71 @@
       <c r="H14" s="19"/>
       <c r="I14" s="18"/>
       <c r="K14" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="29">
         <f>C10/C7</f>
         <v>1.9958611347575517E-3</v>
       </c>
-      <c r="D15" s="16">
-        <f t="shared" ref="D15:H15" si="1">D10/D7</f>
+      <c r="D15" s="29">
+        <f>D10/D7</f>
         <v>1.9977678308833896E-3</v>
       </c>
-      <c r="E15" s="16">
-        <f t="shared" si="1"/>
+      <c r="E15" s="29">
+        <f>E10/E7</f>
         <v>1.9971936899263322E-3</v>
       </c>
-      <c r="F15" s="16">
-        <f t="shared" si="1"/>
+      <c r="F15" s="29">
+        <f>F10/F7</f>
         <v>1.7452005217274901E-3</v>
       </c>
-      <c r="G15" s="16">
-        <f t="shared" si="1"/>
+      <c r="G15" s="29">
+        <f>G10/G7</f>
         <v>1.6924033355141706E-3</v>
       </c>
-      <c r="H15" s="16">
-        <f t="shared" si="1"/>
+      <c r="H15" s="29">
+        <f>H10/H7</f>
         <v>1.6551480268714881E-3</v>
       </c>
-      <c r="I15" s="18"/>
+      <c r="I15" s="16">
+        <f>AVERAGE(C15:H15)</f>
+        <v>1.8472624232800704E-3</v>
+      </c>
       <c r="K15" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="29">
         <f>C13/C7</f>
         <v>2.0097897171468719E-3</v>
       </c>
-      <c r="D16" s="16">
-        <f t="shared" ref="D16:H16" si="2">D13/D7</f>
+      <c r="D16" s="29">
+        <f>D13/D7</f>
         <v>2.0067799925599598E-3</v>
       </c>
-      <c r="E16" s="16">
-        <f t="shared" si="2"/>
+      <c r="E16" s="29">
+        <f>E13/E7</f>
         <v>2.0027672235561475E-3</v>
       </c>
-      <c r="F16" s="16">
-        <f t="shared" si="2"/>
+      <c r="F16" s="29">
+        <f>F13/F7</f>
         <v>1.7595078289116249E-3</v>
       </c>
-      <c r="G16" s="16">
-        <f t="shared" si="2"/>
+      <c r="G16" s="29">
+        <f>G13/G7</f>
         <v>1.7067301537801506E-3</v>
       </c>
-      <c r="H16" s="16">
-        <f t="shared" si="2"/>
+      <c r="H16" s="29">
+        <f>H13/H7</f>
         <v>1.6594731871247344E-3</v>
       </c>
       <c r="I16" s="18"/>
@@ -946,7 +950,7 @@
       <c r="H17" s="19"/>
       <c r="I17" s="18"/>
       <c r="K17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
@@ -982,11 +986,11 @@
         <v>1.3928582389320283E-5</v>
       </c>
       <c r="D19" s="16">
-        <f t="shared" ref="D19:E19" si="3">D11/D7</f>
+        <f>D11/D7</f>
         <v>9.0121616765704616E-6</v>
       </c>
       <c r="E19" s="16">
-        <f t="shared" si="3"/>
+        <f>E11/E7</f>
         <v>5.5735336298150659E-6</v>
       </c>
       <c r="F19" s="16">
@@ -994,11 +998,11 @@
         <v>1.4307307184134673E-5</v>
       </c>
       <c r="G19" s="16">
-        <f t="shared" ref="G19:H19" si="4">G12/G7</f>
+        <f>G12/G7</f>
         <v>1.432681826598004E-5</v>
       </c>
       <c r="H19" s="16">
-        <f t="shared" si="4"/>
+        <f>H12/H7</f>
         <v>4.3251602532463361E-6</v>
       </c>
       <c r="I19" s="16">
@@ -1033,8 +1037,8 @@
         <v>26</v>
       </c>
       <c r="C22" s="26">
-        <f>I6+I19</f>
-        <v>1.8435789272331781E-3</v>
+        <f>I15+I19</f>
+        <v>1.8575080171799149E-3</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -1072,7 +1076,7 @@
       </c>
       <c r="C24" s="17">
         <f>C23-C22</f>
-        <v>1.3064210727668215E-3</v>
+        <v>1.2924919828200846E-3</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
@@ -1113,7 +1117,7 @@
       </c>
       <c r="C27" s="28">
         <f>C26+C24</f>
-        <v>2.9166666666666664E-3</v>
+        <v>2.9027375767199295E-3</v>
       </c>
       <c r="D27" t="s">
         <v>30</v>
